--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,42 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danielito\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ƒUSER\Documents\GitHub\SALIDAS-CORABASTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{106DF3D3-F7FE-49E9-B365-40573068DC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFA140D-B6E5-4863-B238-C84ECD1809AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{4645DC94-C64F-4465-B5F5-5363EF951AA2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="3" xr2:uid="{4645DC94-C64F-4465-B5F5-5363EF951AA2}"/>
   </bookViews>
   <sheets>
     <sheet name="FUNDACION" sheetId="1" r:id="rId1"/>
     <sheet name="ITEMS" sheetId="2" r:id="rId2"/>
+    <sheet name="PLACAS" sheetId="3" r:id="rId3"/>
+    <sheet name="CONDUCTORESSERGIO CHOACHI" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CONDUCTORESSERGIO CHOACHI'!$A$1:$A$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLACAS!$A$1:$A$43</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="1631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="1712">
   <si>
     <t>NIT</t>
   </si>
@@ -4929,13 +4925,256 @@
   </si>
   <si>
     <t>ITEM</t>
+  </si>
+  <si>
+    <t>ERK 690</t>
+  </si>
+  <si>
+    <t>BNW 403</t>
+  </si>
+  <si>
+    <t>EQZ 295</t>
+  </si>
+  <si>
+    <t>EYX 658</t>
+  </si>
+  <si>
+    <t>GES 894</t>
+  </si>
+  <si>
+    <t>GEU 614</t>
+  </si>
+  <si>
+    <t>GZZ 468</t>
+  </si>
+  <si>
+    <t>JUY 943</t>
+  </si>
+  <si>
+    <t>KSP 197</t>
+  </si>
+  <si>
+    <t>KSP 693</t>
+  </si>
+  <si>
+    <t>LQL 137</t>
+  </si>
+  <si>
+    <t>LUN 095</t>
+  </si>
+  <si>
+    <t>LUX 089</t>
+  </si>
+  <si>
+    <t>NNV 230</t>
+  </si>
+  <si>
+    <t>PLACA APOYO</t>
+  </si>
+  <si>
+    <t>SPO 408</t>
+  </si>
+  <si>
+    <t>SVD 736</t>
+  </si>
+  <si>
+    <t>SXZ 622</t>
+  </si>
+  <si>
+    <t>SZV 331</t>
+  </si>
+  <si>
+    <t>TAM 606</t>
+  </si>
+  <si>
+    <t>UPQ 062</t>
+  </si>
+  <si>
+    <t>WCK 306</t>
+  </si>
+  <si>
+    <t>WEP 219</t>
+  </si>
+  <si>
+    <t>WFQ 086</t>
+  </si>
+  <si>
+    <t>WGP 106</t>
+  </si>
+  <si>
+    <t>WGZ 675</t>
+  </si>
+  <si>
+    <t>WLL 341</t>
+  </si>
+  <si>
+    <t>WLM 017</t>
+  </si>
+  <si>
+    <t>WNR 004</t>
+  </si>
+  <si>
+    <t>WOR 660</t>
+  </si>
+  <si>
+    <t>WOU 691</t>
+  </si>
+  <si>
+    <t>WOW926</t>
+  </si>
+  <si>
+    <t>JSL 381</t>
+  </si>
+  <si>
+    <t>POZ 768</t>
+  </si>
+  <si>
+    <t>BRF 156</t>
+  </si>
+  <si>
+    <t>PLACA</t>
+  </si>
+  <si>
+    <t>SERGIO CHOACHI</t>
+  </si>
+  <si>
+    <t>MAURICIO TORO</t>
+  </si>
+  <si>
+    <t>LUIS EBER ORTIZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JEISON QUINTERO</t>
+  </si>
+  <si>
+    <t>OSCAR MARIN</t>
+  </si>
+  <si>
+    <t>JOSE BOTERO</t>
+  </si>
+  <si>
+    <t>LUIS GARZON</t>
+  </si>
+  <si>
+    <t>JORGE PARRA</t>
+  </si>
+  <si>
+    <t>FERNANDO PARRA</t>
+  </si>
+  <si>
+    <t>MISAEL CRUZ</t>
+  </si>
+  <si>
+    <t>DANIEL MARTIN</t>
+  </si>
+  <si>
+    <t>ALVARO GUTIERREZ</t>
+  </si>
+  <si>
+    <t>JHON VARGAS</t>
+  </si>
+  <si>
+    <t>ANDRES LOZANO</t>
+  </si>
+  <si>
+    <t>ANDRES BELTRAN</t>
+  </si>
+  <si>
+    <t>SEBASTIAN ROMERO</t>
+  </si>
+  <si>
+    <t>JOHAN RIVERA</t>
+  </si>
+  <si>
+    <t>JUAN BOHORQUEZ</t>
+  </si>
+  <si>
+    <t>JOSE GUTIERRES</t>
+  </si>
+  <si>
+    <t>DIMAS BELTRAN</t>
+  </si>
+  <si>
+    <t>FERNEY SANCHEZ</t>
+  </si>
+  <si>
+    <t>DIEGO CHOACHI</t>
+  </si>
+  <si>
+    <t>RAFAEL CARDOZO</t>
+  </si>
+  <si>
+    <t>CONDUCTOR APOYO</t>
+  </si>
+  <si>
+    <t>JAIME SUAREZ</t>
+  </si>
+  <si>
+    <t>WILSON PULIDO</t>
+  </si>
+  <si>
+    <t>ALFREDO GUTIERREZ</t>
+  </si>
+  <si>
+    <t>JHON OTALORA</t>
+  </si>
+  <si>
+    <t>JAVIER VARGAS</t>
+  </si>
+  <si>
+    <t>ORLANDO FUENTES</t>
+  </si>
+  <si>
+    <t>JORGE CONTRERAS</t>
+  </si>
+  <si>
+    <t>JHON PEÑA</t>
+  </si>
+  <si>
+    <t>GUSTAVO RIVERA</t>
+  </si>
+  <si>
+    <t>JONATHAN CAMELO</t>
+  </si>
+  <si>
+    <t>JHONATHA CAMELO</t>
+  </si>
+  <si>
+    <t>JULIAN SANTAMARIA</t>
+  </si>
+  <si>
+    <t>JULIAN PEREZ</t>
+  </si>
+  <si>
+    <t>JULIAN LORDUIS</t>
+  </si>
+  <si>
+    <t>HENRY RAMIREZ</t>
+  </si>
+  <si>
+    <t>HUMBERTO AMADO</t>
+  </si>
+  <si>
+    <t>LUIS SABOGAL</t>
+  </si>
+  <si>
+    <t>CESAR PEÑA</t>
+  </si>
+  <si>
+    <t>JHON BELTRAN</t>
+  </si>
+  <si>
+    <t>MAICOL GUERRERO</t>
+  </si>
+  <si>
+    <t>CONDUCTOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4943,16 +5182,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -4960,12 +5212,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18159,4 +18488,448 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819BAF35-06D0-4665-9577-46C832FFD863}">
+  <dimension ref="A1:A37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A43" xr:uid="{819BAF35-06D0-4665-9577-46C832FFD863}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A43">
+      <sortCondition ref="A1:A43"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD7F41F-0743-4A56-925B-1AA80689398F}">
+  <dimension ref="A1:A45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A45" xr:uid="{FFD7F41F-0743-4A56-925B-1AA80689398F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A45">
+      <sortCondition ref="A1:A50"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>